--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.76322057217652</v>
+        <v>7.761523342978685</v>
       </c>
       <c r="D2" t="n">
-        <v>31.36692171029221</v>
+        <v>5.097124777922485</v>
       </c>
       <c r="E2" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F2" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.97244592194264</v>
+        <v>8.770522462315681</v>
       </c>
       <c r="D3" t="n">
-        <v>28.00643196783551</v>
+        <v>4.55104519477327</v>
       </c>
       <c r="E3" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F3" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.13193827235465</v>
+        <v>7.333939969257631</v>
       </c>
       <c r="D4" t="n">
-        <v>35.0726465595016</v>
+        <v>5.699305065919011</v>
       </c>
       <c r="E4" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F4" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.48634571957375</v>
+        <v>7.716531179430734</v>
       </c>
       <c r="D5" t="n">
-        <v>48.29225623052126</v>
+        <v>7.847491637459705</v>
       </c>
       <c r="E5" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F5" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.44068129041021</v>
+        <v>3.80911070969166</v>
       </c>
       <c r="D6" t="n">
-        <v>24.22226522956789</v>
+        <v>3.936118099804783</v>
       </c>
       <c r="E6" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F6" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.48330535163244</v>
+        <v>9.016037119640272</v>
       </c>
       <c r="D7" t="n">
-        <v>53.40072534011624</v>
+        <v>8.677617867768889</v>
       </c>
       <c r="E7" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F7" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.21125115065229</v>
+        <v>7.346828311980998</v>
       </c>
       <c r="D8" t="n">
-        <v>45.4340684608846</v>
+        <v>7.383036124893747</v>
       </c>
       <c r="E8" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F8" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.12942907359788</v>
+        <v>5.708532224459656</v>
       </c>
       <c r="D9" t="n">
-        <v>34.31888716722438</v>
+        <v>5.576819164673962</v>
       </c>
       <c r="E9" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F9" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.36314944145166</v>
+        <v>9.646511784235896</v>
       </c>
       <c r="D10" t="n">
-        <v>59.05022605285603</v>
+        <v>9.595661733589106</v>
       </c>
       <c r="E10" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F10" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>63.77288093890712</v>
+        <v>10.36309315257241</v>
       </c>
       <c r="D11" t="n">
-        <v>60.95092902436027</v>
+        <v>9.904525966458545</v>
       </c>
       <c r="E11" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F11" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>69.66431590487151</v>
+        <v>11.32045133454162</v>
       </c>
       <c r="D12" t="n">
-        <v>66.8410920700632</v>
+        <v>10.86167746138527</v>
       </c>
       <c r="E12" t="n">
-        <v>12.40678102575732</v>
+        <v>2.016101916685565</v>
       </c>
       <c r="F12" t="n">
-        <v>13.89436479122519</v>
+        <v>2.257834278574093</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
